--- a/diseases/d108/2005-2009.xlsx
+++ b/diseases/d108/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.3368880638874524</v>
       </c>
@@ -1705,9 +1699,6 @@
       <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.06489118613301309</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -2645,9 +2633,6 @@
       <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.08652158151068412</v>
       </c>
@@ -3189,9 +3174,6 @@
       <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -3585,9 +3567,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4129,9 +4108,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -4525,9 +4501,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5069,9 +5042,6 @@
       <c r="O25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -5465,9 +5435,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -6009,9 +5976,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6405,9 +6369,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6949,9 +6910,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -7345,9 +7303,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>5</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -8285,9 +8237,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8829,9 +8778,6 @@
       <c r="O45" t="n">
         <v>5</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -9225,9 +9171,6 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -9769,9 +9712,6 @@
       <c r="O50" t="n">
         <v>6</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.1143710677797259</v>
       </c>
@@ -10165,9 +10105,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.06489118613301309</v>
       </c>
@@ -10709,9 +10646,6 @@
       <c r="O55" t="n">
         <v>7</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.1334329124096802</v>
       </c>
@@ -11105,9 +11039,6 @@
       <c r="O57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -11649,9 +11580,6 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -12045,9 +11973,6 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -12589,9 +12514,6 @@
       <c r="O65" t="n">
         <v>6</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.1139331400457613</v>
       </c>
@@ -12985,9 +12907,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13381,9 +13300,6 @@
       <c r="O69" t="n">
         <v>2</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -13925,9 +13841,6 @@
       <c r="O72" t="n">
         <v>3</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -14321,9 +14234,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -14865,9 +14775,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -15261,9 +15168,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -15805,9 +15709,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -16201,9 +16102,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -16745,9 +16643,6 @@
       <c r="O87" t="n">
         <v>9</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.1708997100686419</v>
       </c>
@@ -17141,9 +17036,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -17685,9 +17577,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -18081,9 +17970,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -18625,9 +18511,6 @@
       <c r="O97" t="n">
         <v>4</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -19021,9 +18904,6 @@
       <c r="O99" t="n">
         <v>2</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -19565,9 +19445,6 @@
       <c r="O102" t="n">
         <v>4</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -19961,9 +19838,6 @@
       <c r="O104" t="n">
         <v>6</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.1287417170797774</v>
       </c>
@@ -20505,9 +20379,6 @@
       <c r="O107" t="n">
         <v>2</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -20901,9 +20772,6 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -21445,9 +21313,6 @@
       <c r="O112" t="n">
         <v>3</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -21841,9 +21706,6 @@
       <c r="O114" t="n">
         <v>3</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.06437085853988869</v>
       </c>
@@ -22385,9 +22247,6 @@
       <c r="O117" t="n">
         <v>9</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.1708997100686419</v>
       </c>
@@ -22781,9 +22640,6 @@
       <c r="O119" t="n">
         <v>5</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.1072847642331478</v>
       </c>
@@ -23325,9 +23181,6 @@
       <c r="O122" t="n">
         <v>3</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -23721,9 +23574,6 @@
       <c r="O124" t="n">
         <v>5</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.1072847642331478</v>
       </c>
@@ -24265,9 +24115,6 @@
       <c r="O127" t="n">
         <v>5</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.09454101283677872</v>
       </c>
@@ -24661,9 +24508,6 @@
       <c r="O129" t="n">
         <v>4</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>1.283489036597085</v>
       </c>
@@ -25057,9 +24901,6 @@
       <c r="O131" t="n">
         <v>7</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.1486512026944092</v>
       </c>
@@ -25601,9 +25442,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -25997,9 +25835,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -26541,9 +26376,6 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -26937,9 +26769,6 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -27481,9 +27310,6 @@
       <c r="O144" t="n">
         <v>3</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -27877,9 +27703,6 @@
       <c r="O146" t="n">
         <v>1</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -28421,9 +28244,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -28817,9 +28637,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -29361,9 +29178,6 @@
       <c r="O154" t="n">
         <v>4</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -29757,9 +29571,6 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -30301,9 +30112,6 @@
       <c r="O159" t="n">
         <v>3</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -30697,9 +30505,6 @@
       <c r="O161" t="n">
         <v>4</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -31241,9 +31046,6 @@
       <c r="O164" t="n">
         <v>6</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.1134492154041345</v>
       </c>
@@ -31637,9 +31439,6 @@
       <c r="O166" t="n">
         <v>2</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -32181,9 +31980,6 @@
       <c r="O169" t="n">
         <v>5</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.09454101283677872</v>
       </c>
@@ -32577,9 +32373,6 @@
       <c r="O171" t="n">
         <v>5</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.1061794304960066</v>
       </c>
@@ -33121,9 +32914,6 @@
       <c r="O174" t="n">
         <v>5</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.09454101283677872</v>
       </c>
@@ -33517,9 +33307,6 @@
       <c r="O176" t="n">
         <v>23</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.4884253802816304</v>
       </c>
@@ -34061,9 +33848,6 @@
       <c r="O179" t="n">
         <v>2</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -34457,9 +34241,6 @@
       <c r="O181" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -35001,9 +34782,6 @@
       <c r="O184" t="n">
         <v>6</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.1134492154041345</v>
       </c>
@@ -35397,9 +35175,6 @@
       <c r="O186" t="n">
         <v>2</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -35941,9 +35716,6 @@
       <c r="O189" t="n">
         <v>5</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -36337,9 +36109,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -36733,9 +36502,6 @@
       <c r="O193" t="n">
         <v>3</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.06291813029967276</v>
       </c>
@@ -37277,9 +37043,6 @@
       <c r="O196" t="n">
         <v>2</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -37673,9 +37436,6 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -38217,9 +37977,6 @@
       <c r="O201" t="n">
         <v>2</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -38613,9 +38370,6 @@
       <c r="O203" t="n">
         <v>1</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -39157,9 +38911,6 @@
       <c r="O206" t="n">
         <v>6</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.1129225349528181</v>
       </c>
@@ -39553,9 +39304,6 @@
       <c r="O208" t="n">
         <v>2</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -40097,9 +39845,6 @@
       <c r="O211" t="n">
         <v>4</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.07528168996854542</v>
       </c>
@@ -40493,9 +40238,6 @@
       <c r="O213" t="n">
         <v>5</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -41037,9 +40779,6 @@
       <c r="O216" t="n">
         <v>1</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -41433,9 +41172,6 @@
       <c r="O218" t="n">
         <v>2</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -41977,9 +41713,6 @@
       <c r="O221" t="n">
         <v>2</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -42521,9 +42254,6 @@
       <c r="O224" t="n">
         <v>1</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -43065,9 +42795,6 @@
       <c r="O227" t="n">
         <v>2</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -43609,9 +43336,6 @@
       <c r="O230" t="n">
         <v>5</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -44153,9 +43877,6 @@
       <c r="O233" t="n">
         <v>5</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -44697,9 +44418,6 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -45241,9 +44959,6 @@
       <c r="O239" t="n">
         <v>5</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -45785,9 +45500,6 @@
       <c r="O242" t="n">
         <v>8</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.1677816807991274</v>
       </c>
@@ -46329,9 +46041,6 @@
       <c r="O245" t="n">
         <v>1</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -46873,9 +46582,6 @@
       <c r="O248" t="n">
         <v>3</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.06291813029967276</v>
       </c>
@@ -47417,9 +47123,6 @@
       <c r="O251" t="n">
         <v>5</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -47961,9 +47664,6 @@
       <c r="O254" t="n">
         <v>2</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -48505,9 +48205,6 @@
       <c r="O257" t="n">
         <v>8</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.1498448216392405</v>
       </c>
@@ -49049,9 +48746,6 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -49445,9 +49139,6 @@
       <c r="O262" t="n">
         <v>5</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.1035492006260585</v>
       </c>
@@ -49989,9 +49680,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -50533,9 +50221,6 @@
       <c r="O268" t="n">
         <v>1</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -51077,9 +50762,6 @@
       <c r="O271" t="n">
         <v>2</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -51621,9 +51303,6 @@
       <c r="O274" t="n">
         <v>3</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.06212952037563508</v>
       </c>
@@ -52165,9 +51844,6 @@
       <c r="O277" t="n">
         <v>1</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -52709,9 +52385,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -53253,9 +52926,6 @@
       <c r="O283" t="n">
         <v>4</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -53797,9 +53467,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -54341,9 +54008,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -54885,9 +54549,6 @@
       <c r="O292" t="n">
         <v>4</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.08283936050084678</v>
       </c>
@@ -55429,9 +55090,6 @@
       <c r="O295" t="n">
         <v>2</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -55973,9 +55631,6 @@
       <c r="O298" t="n">
         <v>5</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.1035492006260585</v>
       </c>
@@ -56517,9 +56172,6 @@
       <c r="O301" t="n">
         <v>2</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -57061,9 +56713,6 @@
       <c r="O304" t="n">
         <v>2</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -57605,9 +57254,6 @@
       <c r="O307" t="n">
         <v>7</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0.1311142189343355</v>
       </c>
@@ -58149,9 +57795,6 @@
       <c r="O310" t="n">
         <v>4</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.08283936050084678</v>
       </c>
@@ -58693,9 +58336,6 @@
       <c r="O313" t="n">
         <v>1</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -59237,9 +58877,6 @@
       <c r="O316" t="n">
         <v>2</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -59781,9 +59418,6 @@
       <c r="O319" t="n">
         <v>1</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -60325,9 +59959,6 @@
       <c r="O322" t="n">
         <v>4</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0.08283936050084678</v>
       </c>
@@ -60869,9 +60500,6 @@
       <c r="O325" t="n">
         <v>6</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0.1123836162294304</v>
       </c>
@@ -61412,9 +61040,6 @@
       </c>
       <c r="O328" t="n">
         <v>1</v>
-      </c>
-      <c r="Q328" t="n">
-        <v>0</v>
       </c>
       <c r="R328" t="n">
         <v>0.0207098401252117</v>
